--- a/Faydalanma Atama/Kılavuz.xlsx
+++ b/Faydalanma Atama/Kılavuz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Faydalanma Atama\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F1A0DFE-4C25-4B3D-962B-B155198203BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E35B44A-7A9C-4219-A5EF-C741D28C71E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="270">
   <si>
     <t>KAYITLI SEÇİM</t>
   </si>
@@ -139,703 +139,697 @@
     <t>KATLI LOT</t>
   </si>
   <si>
-    <t>1100003308000010</t>
-  </si>
-  <si>
-    <t>ATASAN METAL SAN.</t>
-  </si>
-  <si>
-    <t>000000000040000151</t>
-  </si>
-  <si>
-    <t>2.40MM-CT-SH (196) YAGSIZ (ATASAN)</t>
+    <t>M00000680</t>
+  </si>
+  <si>
+    <t>MAKE TO STOCK</t>
+  </si>
+  <si>
+    <t>000000000040002586</t>
+  </si>
+  <si>
+    <t>PRV 1.50MM-83HC</t>
+  </si>
+  <si>
+    <t>DB820</t>
+  </si>
+  <si>
+    <t>M187</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>1.50</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>83HC</t>
+  </si>
+  <si>
+    <t>1100003158000010</t>
+  </si>
+  <si>
+    <t>GÜVEN ÇELİK HALAT INS. ASANS.OTOM.SAN.TIC.LTD.STI.</t>
+  </si>
+  <si>
+    <t>000000000040000833</t>
+  </si>
+  <si>
+    <t>HT 0.78MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>DB355</t>
+  </si>
+  <si>
+    <t>M171</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>KY180</t>
+  </si>
+  <si>
+    <t>000000000040000827</t>
+  </si>
+  <si>
+    <t>HT 0.66MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>M191</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>000000000040000826</t>
+  </si>
+  <si>
+    <t>HT 0.64MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>M125</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>1100003572000010</t>
+  </si>
+  <si>
+    <t>000000000040000828</t>
+  </si>
+  <si>
+    <t>HT 0.68MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>DB630</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>000000000040000823</t>
+  </si>
+  <si>
+    <t>HT 0.58MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>M123</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>000000000040000820</t>
+  </si>
+  <si>
+    <t>HT 0.52MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>DB250</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>000000000040000848</t>
+  </si>
+  <si>
+    <t>HT 1.10MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>1.10</t>
+  </si>
+  <si>
+    <t>000000000040000825</t>
+  </si>
+  <si>
+    <t>HT 0.62MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>000000000040000822</t>
+  </si>
+  <si>
+    <t>HT 0.56MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>000000000040000815</t>
+  </si>
+  <si>
+    <t>HT 0.42MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>M121</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>1100003584000010</t>
+  </si>
+  <si>
+    <t>EFEOĞLU ÇELİK HALAT LTD.ŞTİ.</t>
+  </si>
+  <si>
+    <t>000000000040000844</t>
+  </si>
+  <si>
+    <t>HT 1.00MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>DB400</t>
+  </si>
+  <si>
+    <t>M189</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>000000000040000836</t>
+  </si>
+  <si>
+    <t>HT 0.84MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>M172</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>1100003583000010</t>
+  </si>
+  <si>
+    <t>M126</t>
+  </si>
+  <si>
+    <t>000000000040000818</t>
+  </si>
+  <si>
+    <t>HT 0.48MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>1100003579000040</t>
+  </si>
+  <si>
+    <t>REDAELLI TECNA S.P.A. DIV.TECI</t>
+  </si>
+  <si>
+    <t>000000000040001726</t>
+  </si>
+  <si>
+    <t>HT 1.03MM-CT-KY210</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>KY210</t>
+  </si>
+  <si>
+    <t>1100003586000010</t>
+  </si>
+  <si>
+    <t>000000000040002071</t>
+  </si>
+  <si>
+    <t>HT 1.23MM-KT_B-KY220</t>
+  </si>
+  <si>
+    <t>M116</t>
+  </si>
+  <si>
+    <t>1.23</t>
+  </si>
+  <si>
+    <t>KT_B</t>
+  </si>
+  <si>
+    <t>KY220</t>
+  </si>
+  <si>
+    <t>1100003627000030</t>
+  </si>
+  <si>
+    <t>UZMAN YAY MAKİNA SANAYİ A.Ş.</t>
+  </si>
+  <si>
+    <t>000000000040002966</t>
+  </si>
+  <si>
+    <t>2.60MM-CT-DH (193) YAGLI (UZMAN)</t>
   </si>
   <si>
     <t>KANGAL</t>
   </si>
   <si>
+    <t>M199</t>
+  </si>
+  <si>
+    <t>2.60</t>
+  </si>
+  <si>
+    <t>YY</t>
+  </si>
+  <si>
+    <t>YAGLI</t>
+  </si>
+  <si>
+    <t>DH</t>
+  </si>
+  <si>
+    <t>1100003636000010</t>
+  </si>
+  <si>
+    <t>000000000040000845</t>
+  </si>
+  <si>
+    <t>HT 1.03MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>000000000040000839</t>
+  </si>
+  <si>
+    <t>HT 0.90MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>1100003717000100</t>
+  </si>
+  <si>
+    <t>000000000040000150</t>
+  </si>
+  <si>
+    <t>2.40MM-CT-SH (196) YAGLI</t>
+  </si>
+  <si>
+    <t>2.40</t>
+  </si>
+  <si>
+    <t>SH</t>
+  </si>
+  <si>
+    <t>1100003728000010</t>
+  </si>
+  <si>
+    <t>KAPTAN ÇELİK HALAT A.Ş.</t>
+  </si>
+  <si>
+    <t>000000000040000750</t>
+  </si>
+  <si>
+    <t>HT 1.75MM-KT_B-KY160</t>
+  </si>
+  <si>
+    <t>M184</t>
+  </si>
+  <si>
+    <t>1.75</t>
+  </si>
+  <si>
+    <t>KY160</t>
+  </si>
+  <si>
+    <t>1100003754000020</t>
+  </si>
+  <si>
+    <t>BİLAL PARS YAPI İNŞAAT LTD. ŞTİ.</t>
+  </si>
+  <si>
+    <t>000000000040001361</t>
+  </si>
+  <si>
+    <t>HT 0.94MM-CT-KY200</t>
+  </si>
+  <si>
+    <t>M188</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>KY200</t>
+  </si>
+  <si>
+    <t>1100003754000010</t>
+  </si>
+  <si>
+    <t>000000000040001364</t>
+  </si>
+  <si>
+    <t>HT 1.00MM-CT-KY200</t>
+  </si>
+  <si>
+    <t>1100003760000010</t>
+  </si>
+  <si>
+    <t>EURORED VIGO S.L.</t>
+  </si>
+  <si>
+    <t>000000000040000656</t>
+  </si>
+  <si>
+    <t>HT 2.05MM-KT_AB-KY160</t>
+  </si>
+  <si>
+    <t>M181</t>
+  </si>
+  <si>
+    <t>2.05</t>
+  </si>
+  <si>
+    <t>KT_AB</t>
+  </si>
+  <si>
+    <t>1100003786000070</t>
+  </si>
+  <si>
+    <t>CORDERIE DOR MAROC</t>
+  </si>
+  <si>
+    <t>000000000040002057</t>
+  </si>
+  <si>
+    <t>HT 0.90MM-KT_B-KY220</t>
+  </si>
+  <si>
+    <t>M173</t>
+  </si>
+  <si>
+    <t>1100003803000040</t>
+  </si>
+  <si>
+    <t>SOUTHERN WIRE, LLC</t>
+  </si>
+  <si>
+    <t>000000000040001380</t>
+  </si>
+  <si>
+    <t>HT 1.40MM-CT-KY200</t>
+  </si>
+  <si>
+    <t>M177</t>
+  </si>
+  <si>
+    <t>1.40</t>
+  </si>
+  <si>
+    <t>1100003787000060</t>
+  </si>
+  <si>
+    <t>KULKONI INC.</t>
+  </si>
+  <si>
+    <t>000000000040001377</t>
+  </si>
+  <si>
+    <t>HT 1.33MM-CT-KY200</t>
+  </si>
+  <si>
+    <t>M195</t>
+  </si>
+  <si>
+    <t>1.33</t>
+  </si>
+  <si>
+    <t>000000000040001378</t>
+  </si>
+  <si>
+    <t>HT 1.35MM-CT-KY200</t>
+  </si>
+  <si>
+    <t>1.35</t>
+  </si>
+  <si>
+    <t>000000000040001376</t>
+  </si>
+  <si>
+    <t>HT 1.30MM-CT-KY200</t>
+  </si>
+  <si>
+    <t>1.30</t>
+  </si>
+  <si>
+    <t>1100003803000050</t>
+  </si>
+  <si>
+    <t>000000000040001384</t>
+  </si>
+  <si>
+    <t>HT 1.50MM-CT-KY200</t>
+  </si>
+  <si>
+    <t>000000000040001382</t>
+  </si>
+  <si>
+    <t>HT 1.45MM-CT-KY200</t>
+  </si>
+  <si>
+    <t>M186</t>
+  </si>
+  <si>
+    <t>1.45</t>
+  </si>
+  <si>
+    <t>1100003780000010</t>
+  </si>
+  <si>
+    <t>000000000040001132</t>
+  </si>
+  <si>
+    <t>HT 1.65MM-KT_B-KY180</t>
+  </si>
+  <si>
+    <t>M170</t>
+  </si>
+  <si>
+    <t>1.65</t>
+  </si>
+  <si>
+    <t>000000000040001123</t>
+  </si>
+  <si>
+    <t>HT 1.43MM-KT_B-KY180</t>
+  </si>
+  <si>
+    <t>1.43</t>
+  </si>
+  <si>
+    <t>1100003780000020</t>
+  </si>
+  <si>
+    <t>000000000040001098</t>
+  </si>
+  <si>
+    <t>HT 0.84MM-KT_B-KY180</t>
+  </si>
+  <si>
+    <t>M198</t>
+  </si>
+  <si>
+    <t>000000000040000870</t>
+  </si>
+  <si>
+    <t>HT 1.65MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>1100003780000040</t>
+  </si>
+  <si>
+    <t>1100003780000050</t>
+  </si>
+  <si>
     <t>M178</t>
   </si>
   <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>2.40</t>
-  </si>
-  <si>
-    <t>TC</t>
-  </si>
-  <si>
-    <t>YY</t>
-  </si>
-  <si>
-    <t>YAGSIZ</t>
-  </si>
-  <si>
-    <t>CT</t>
-  </si>
-  <si>
-    <t>SH</t>
-  </si>
-  <si>
-    <t>1100003515000040</t>
-  </si>
-  <si>
-    <t>TELBANT PAZARLAMA İTH.VE TİC.</t>
-  </si>
-  <si>
-    <t>000000000040000472</t>
-  </si>
-  <si>
-    <t>1.70MM-KT_C-SM (185)</t>
-  </si>
-  <si>
-    <t>M170</t>
-  </si>
-  <si>
-    <t>1.70</t>
-  </si>
-  <si>
-    <t>KT_C</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>1100003543000120</t>
-  </si>
-  <si>
-    <t>GÜVEN ÇELİK HALAT INS. ASANS.OTOM.SAN.TIC.LTD.STI.</t>
-  </si>
-  <si>
-    <t>000000000040000857</t>
-  </si>
-  <si>
-    <t>HT 1.33MM-CT-KY180</t>
-  </si>
-  <si>
-    <t>DB400</t>
-  </si>
-  <si>
-    <t>M193</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>1.33</t>
-  </si>
-  <si>
-    <t>KY180</t>
-  </si>
-  <si>
-    <t>1100003548000010</t>
-  </si>
-  <si>
-    <t>Platzmann federn gmbh &amp; co. kg</t>
-  </si>
-  <si>
-    <t>000000000040000450</t>
-  </si>
-  <si>
-    <t>4.00MM-KT_C-SH (177)</t>
-  </si>
-  <si>
-    <t>Z5-5</t>
-  </si>
-  <si>
-    <t>M160</t>
-  </si>
-  <si>
-    <t>4.00</t>
-  </si>
-  <si>
-    <t>1100003580000080</t>
-  </si>
-  <si>
-    <t>REDAELLI TECNA S.P.A. DIV.TECI</t>
-  </si>
-  <si>
-    <t>000000000040001386</t>
-  </si>
-  <si>
-    <t>HT 1.55MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>M177</t>
-  </si>
-  <si>
-    <t>1.55</t>
-  </si>
-  <si>
-    <t>KY200</t>
-  </si>
-  <si>
-    <t>1100003580000060</t>
-  </si>
-  <si>
-    <t>000000000040001380</t>
-  </si>
-  <si>
-    <t>HT 1.40MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>DB630</t>
-  </si>
-  <si>
-    <t>M116</t>
-  </si>
-  <si>
-    <t>1.40</t>
-  </si>
-  <si>
-    <t>000000000040001379</t>
-  </si>
-  <si>
-    <t>HT 1.38MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>1.38</t>
-  </si>
-  <si>
-    <t>1100003579000060</t>
-  </si>
-  <si>
-    <t>000000000040001385</t>
-  </si>
-  <si>
-    <t>HT 1.53MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>M176</t>
-  </si>
-  <si>
-    <t>1.53</t>
-  </si>
-  <si>
-    <t>1100003579000050</t>
-  </si>
-  <si>
-    <t>000000000040001409</t>
-  </si>
-  <si>
-    <t>HT 2.13MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>M199</t>
-  </si>
-  <si>
-    <t>2.13</t>
-  </si>
-  <si>
-    <t>1100003578000040</t>
-  </si>
-  <si>
-    <t>1100003578000030</t>
-  </si>
-  <si>
-    <t>000000000040001363</t>
-  </si>
-  <si>
-    <t>HT 0.98MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>M171</t>
+    <t>1100003779000040</t>
+  </si>
+  <si>
+    <t>CABLES Y ESLINGAS, S.L.</t>
+  </si>
+  <si>
+    <t>000000000040000987</t>
+  </si>
+  <si>
+    <t>HT 1.00MM-KT_AB-KY180</t>
+  </si>
+  <si>
+    <t>1100003779000090</t>
+  </si>
+  <si>
+    <t>000000000040000986</t>
+  </si>
+  <si>
+    <t>HT 0.98MM-KT_AB-KY180</t>
+  </si>
+  <si>
+    <t>M196</t>
   </si>
   <si>
     <t>0.98</t>
   </si>
   <si>
-    <t>000000000040001384</t>
-  </si>
-  <si>
-    <t>HT 1.50MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>1.50</t>
-  </si>
-  <si>
-    <t>1100003586000010</t>
-  </si>
-  <si>
-    <t>000000000040002061</t>
-  </si>
-  <si>
-    <t>HT 0.98MM-KT_B-KY220</t>
-  </si>
-  <si>
-    <t>M173</t>
-  </si>
-  <si>
-    <t>KT_B</t>
-  </si>
-  <si>
-    <t>KY220</t>
-  </si>
-  <si>
-    <t>000000000040002079</t>
-  </si>
-  <si>
-    <t>HT 1.43MM-KT_B-KY220</t>
-  </si>
-  <si>
-    <t>DB355</t>
-  </si>
-  <si>
-    <t>M187</t>
-  </si>
-  <si>
-    <t>1.43</t>
-  </si>
-  <si>
-    <t>1100003601000030</t>
-  </si>
-  <si>
-    <t>000000000040000835</t>
-  </si>
-  <si>
-    <t>HT 0.82MM-CT-KY180</t>
-  </si>
-  <si>
-    <t>M186</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
-    <t>1100003615000030</t>
-  </si>
-  <si>
-    <t>MAKTEL MAKİNA VE TEL SAN.A.Ş.</t>
-  </si>
-  <si>
-    <t>000000000040000231</t>
-  </si>
-  <si>
-    <t>2.40MM-CT-SH (196) YAGSIZ</t>
-  </si>
-  <si>
-    <t>Z2</t>
-  </si>
-  <si>
-    <t>1100003640000010</t>
-  </si>
-  <si>
-    <t>EFEOĞLU ÇELİK HALAT LTD.ŞTİ.</t>
-  </si>
-  <si>
-    <t>000000000040000132</t>
-  </si>
-  <si>
-    <t>1.70MM-CT-SH (208) YAGLI</t>
-  </si>
-  <si>
-    <t>YAGLI</t>
-  </si>
-  <si>
-    <t>1100003652000010</t>
-  </si>
-  <si>
-    <t>Alser CAPITAL SRL</t>
-  </si>
-  <si>
-    <t>000000000040001343</t>
-  </si>
-  <si>
-    <t>HT 0.58MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>M127</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>000000000040001362</t>
-  </si>
-  <si>
-    <t>HT 0.96MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>0.96</t>
-  </si>
-  <si>
-    <t>1100003672000010</t>
-  </si>
-  <si>
-    <t>SPANSET</t>
-  </si>
-  <si>
-    <t>000000000040000500</t>
-  </si>
-  <si>
-    <t>HT 0.72MM-CT-KY140</t>
-  </si>
-  <si>
-    <t>DB250</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>KY140</t>
-  </si>
-  <si>
-    <t>1100003688000010</t>
-  </si>
-  <si>
-    <t>EURORED VIGO S.L.</t>
-  </si>
-  <si>
-    <t>000000000040001676</t>
-  </si>
-  <si>
-    <t>HT 3.35MM-KT_B-KY200</t>
-  </si>
-  <si>
-    <t>DB750</t>
+    <t>000000000040000984</t>
+  </si>
+  <si>
+    <t>HT 0.94MM-KT_AB-KY180</t>
+  </si>
+  <si>
+    <t>000000000040000989</t>
+  </si>
+  <si>
+    <t>HT 1.05MM-KT_AB-KY180</t>
+  </si>
+  <si>
+    <t>M192</t>
+  </si>
+  <si>
+    <t>1.05</t>
+  </si>
+  <si>
+    <t>1100003788000020</t>
+  </si>
+  <si>
+    <t>ALIOTO GROUP S.R.L</t>
+  </si>
+  <si>
+    <t>000000000040001598</t>
+  </si>
+  <si>
+    <t>HT 0.98MM-KT_B-KY200</t>
+  </si>
+  <si>
+    <t>M190</t>
+  </si>
+  <si>
+    <t>000000000040003444</t>
+  </si>
+  <si>
+    <t>HT 1.05MM-KT_B-KY210</t>
+  </si>
+  <si>
+    <t>M197</t>
+  </si>
+  <si>
+    <t>1100003801000010</t>
+  </si>
+  <si>
+    <t>000000000040000614</t>
+  </si>
+  <si>
+    <t>HT 1.00MM-KT_AB-KY160</t>
+  </si>
+  <si>
+    <t>1100003806000040</t>
+  </si>
+  <si>
+    <t>ÇELİK HALAT VE TEL SANAYİ</t>
+  </si>
+  <si>
+    <t>000000000040000832</t>
+  </si>
+  <si>
+    <t>HT 0.76MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>000000000040000831</t>
+  </si>
+  <si>
+    <t>HT 0.74MM-CT-KY180</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>000000000040001366</t>
+  </si>
+  <si>
+    <t>HT 1.05MM-CT-KY200</t>
+  </si>
+  <si>
+    <t>000000000040001338</t>
+  </si>
+  <si>
+    <t>HT 0.48MM-CT-KY200</t>
+  </si>
+  <si>
+    <t>1100003788000120</t>
+  </si>
+  <si>
+    <t>000000000040002100</t>
+  </si>
+  <si>
+    <t>HT 1.95MM-KT_B-KY220</t>
+  </si>
+  <si>
+    <t>1.95</t>
+  </si>
+  <si>
+    <t>1100003788000110</t>
+  </si>
+  <si>
+    <t>1100003788000050</t>
+  </si>
+  <si>
+    <t>000000000040002102</t>
+  </si>
+  <si>
+    <t>HT 2.00MM-KT_B-KY220</t>
+  </si>
+  <si>
+    <t>2.00</t>
+  </si>
+  <si>
+    <t>000000000040002089</t>
+  </si>
+  <si>
+    <t>HT 1.68MM-KT_B-KY220</t>
   </si>
   <si>
     <t>M185</t>
   </si>
   <si>
-    <t>3.35</t>
-  </si>
-  <si>
-    <t>1100003686000060</t>
-  </si>
-  <si>
-    <t>SOUTHERN WIRE, LLC</t>
-  </si>
-  <si>
-    <t>000000000040001397</t>
-  </si>
-  <si>
-    <t>HT 1.83MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>DB800</t>
-  </si>
-  <si>
-    <t>1.83</t>
-  </si>
-  <si>
-    <t>1100003686000020</t>
-  </si>
-  <si>
-    <t>000000000040001355</t>
-  </si>
-  <si>
-    <t>HT 0.82MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>M198</t>
-  </si>
-  <si>
-    <t>1100003705000080</t>
-  </si>
-  <si>
-    <t>CONTINENTAL CHAIN&amp;RIGGING LTD.</t>
-  </si>
-  <si>
-    <t>000000000040001333</t>
-  </si>
-  <si>
-    <t>HT 0.38MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>M123</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>1100003705000070</t>
-  </si>
-  <si>
-    <t>000000000040001350</t>
-  </si>
-  <si>
-    <t>HT 0.72MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>M172</t>
-  </si>
-  <si>
-    <t>000000000040001349</t>
-  </si>
-  <si>
-    <t>HT 0.70MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>000000000040001346</t>
-  </si>
-  <si>
-    <t>HT 0.64MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>0.64</t>
-  </si>
-  <si>
-    <t>1100003705000060</t>
-  </si>
-  <si>
-    <t>000000000040001412</t>
-  </si>
-  <si>
-    <t>HT 2.20MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>2.20</t>
-  </si>
-  <si>
-    <t>1100003705000040</t>
-  </si>
-  <si>
-    <t>1100003705000030</t>
-  </si>
-  <si>
-    <t>000000000040000875</t>
-  </si>
-  <si>
-    <t>HT 1.78MM-CT-KY180</t>
-  </si>
-  <si>
-    <t>1.78</t>
-  </si>
-  <si>
-    <t>1100003705000020</t>
-  </si>
-  <si>
-    <t>000000000040000894</t>
-  </si>
-  <si>
-    <t>HT 2.25MM-CT-KY180</t>
-  </si>
-  <si>
-    <t>2.25</t>
-  </si>
-  <si>
-    <t>000000000040000851</t>
-  </si>
-  <si>
-    <t>HT 1.18MM-CT-KY180</t>
-  </si>
-  <si>
-    <t>M195</t>
-  </si>
-  <si>
-    <t>1.18</t>
-  </si>
-  <si>
-    <t>000000000040000879</t>
-  </si>
-  <si>
-    <t>HT 1.88MM-CT-KY180</t>
-  </si>
-  <si>
-    <t>1.88</t>
-  </si>
-  <si>
-    <t>1100003705000010</t>
-  </si>
-  <si>
-    <t>1100003715000010</t>
-  </si>
-  <si>
-    <t>HAASE GESMBH</t>
-  </si>
-  <si>
-    <t>000000000040000822</t>
-  </si>
-  <si>
-    <t>HT 0.56MM-CT-KY180</t>
-  </si>
-  <si>
-    <t>M122</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>000000000040000827</t>
-  </si>
-  <si>
-    <t>HT 0.66MM-CT-KY180</t>
-  </si>
-  <si>
-    <t>M132</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>000000000040000820</t>
-  </si>
-  <si>
-    <t>HT 0.52MM-CT-KY180</t>
-  </si>
-  <si>
-    <t>M131</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>000000000040000841</t>
-  </si>
-  <si>
-    <t>HT 0.94MM-CT-KY180</t>
-  </si>
-  <si>
-    <t>M189</t>
-  </si>
-  <si>
-    <t>0.94</t>
-  </si>
-  <si>
-    <t>1100003716000010</t>
-  </si>
-  <si>
-    <t>000000000040000845</t>
-  </si>
-  <si>
-    <t>HT 1.03MM-CT-KY180</t>
-  </si>
-  <si>
-    <t>M188</t>
-  </si>
-  <si>
-    <t>1.03</t>
-  </si>
-  <si>
-    <t>1100003723000070</t>
-  </si>
-  <si>
-    <t>KAPTAN ÇELİK HALAT A.Ş.</t>
-  </si>
-  <si>
-    <t>000000000040000771</t>
-  </si>
-  <si>
-    <t>HT 2.28MM-KT_B-KY160</t>
-  </si>
-  <si>
-    <t>2.28</t>
-  </si>
-  <si>
-    <t>KY160</t>
-  </si>
-  <si>
-    <t>1100003723000060</t>
-  </si>
-  <si>
-    <t>000000000040000750</t>
-  </si>
-  <si>
-    <t>HT 1.75MM-KT_B-KY160</t>
-  </si>
-  <si>
-    <t>M184</t>
-  </si>
-  <si>
-    <t>1.75</t>
-  </si>
-  <si>
-    <t>1100003723000040</t>
-  </si>
-  <si>
-    <t>000000000040000748</t>
-  </si>
-  <si>
-    <t>HT 1.70MM-KT_B-KY160</t>
-  </si>
-  <si>
-    <t>1100003723000030</t>
-  </si>
-  <si>
-    <t>000000000040000630</t>
-  </si>
-  <si>
-    <t>HT 1.40MM-KT_AB-KY160</t>
-  </si>
-  <si>
-    <t>KT_AB</t>
-  </si>
-  <si>
-    <t>1100003723000010</t>
-  </si>
-  <si>
-    <t>000000000040000616</t>
-  </si>
-  <si>
-    <t>HT 1.05MM-KT_AB-KY160</t>
-  </si>
-  <si>
-    <t>M196</t>
-  </si>
-  <si>
-    <t>1.05</t>
-  </si>
-  <si>
-    <t>1100003723000050</t>
-  </si>
-  <si>
-    <t>000000000040000756</t>
-  </si>
-  <si>
-    <t>HT 1.90MM-KT_B-KY160</t>
-  </si>
-  <si>
-    <t>1.90</t>
-  </si>
-  <si>
-    <t>000000000040000716</t>
-  </si>
-  <si>
-    <t>HT 0.92MM-KT_B-KY160</t>
-  </si>
-  <si>
-    <t>0.92</t>
-  </si>
-  <si>
-    <t>000000000040000744</t>
-  </si>
-  <si>
-    <t>HT 1.60MM-KT_B-KY160</t>
-  </si>
-  <si>
-    <t>1.60</t>
-  </si>
-  <si>
-    <t>1100003670000030</t>
-  </si>
-  <si>
-    <t>WALLINGFORDS INC U.S.A</t>
-  </si>
-  <si>
-    <t>000000000040001341</t>
-  </si>
-  <si>
-    <t>HT 0.54MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>M126</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>000000000040001370</t>
-  </si>
-  <si>
-    <t>HT 1.15MM-CT-KY200</t>
-  </si>
-  <si>
-    <t>1.15</t>
+    <t>1.68</t>
+  </si>
+  <si>
+    <t>1100003788000040</t>
+  </si>
+  <si>
+    <t>1100003786000120</t>
+  </si>
+  <si>
+    <t>000000000040003461</t>
+  </si>
+  <si>
+    <t>HT 2.35MM-CT-KY200</t>
+  </si>
+  <si>
+    <t>2.35</t>
   </si>
 </sst>
 </file>
@@ -880,7 +874,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{961DE98A-380D-4181-8587-D515C7446B76}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{8DB41D87-F2A4-4ACE-9864-384B7A59AFE6}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -894,8 +888,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AM55">
-  <autoFilter ref="A1:AM55" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AM63">
+  <autoFilter ref="A1:AM63" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="39">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="KAYITLI SEÇİM"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="SİPARİŞ KODU"/>
@@ -1258,7 +1252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM55"/>
+  <dimension ref="A1:AM63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="11" width="9.140625" style="1" customWidth="1"/>
@@ -1394,7 +1388,7 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>849200</v>
+        <v>674060</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1412,13 +1406,13 @@
         <v>44</v>
       </c>
       <c r="J2" s="1">
-        <v>45991</v>
+        <v>45294.576412037</v>
       </c>
       <c r="K2" s="1">
-        <v>45991</v>
+        <v>45294.576412037</v>
       </c>
       <c r="L2">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="b">
         <v>0</v>
@@ -1427,7 +1421,7 @@
         <v>5</v>
       </c>
       <c r="O2">
-        <v>5631.8</v>
+        <v>72087</v>
       </c>
       <c r="P2" t="s">
         <v>45</v>
@@ -1441,26 +1435,20 @@
       <c r="Y2" t="s">
         <v>45</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AE2" t="s">
         <v>48</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="s">
         <v>49</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>51</v>
       </c>
       <c r="AM2">
         <v>0</v>
@@ -1471,49 +1459,49 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3">
+        <v>841381</v>
+      </c>
+      <c r="E3">
+        <v>841376</v>
+      </c>
+      <c r="F3" t="s">
         <v>52</v>
       </c>
-      <c r="C3" t="s">
+      <c r="G3" t="s">
         <v>53</v>
       </c>
-      <c r="D3">
-        <v>860925</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>54</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>55</v>
       </c>
-      <c r="H3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" t="s">
-        <v>56</v>
-      </c>
       <c r="J3" s="1">
-        <v>45991</v>
+        <v>45930</v>
       </c>
       <c r="K3" s="1">
-        <v>45991</v>
+        <v>45930</v>
       </c>
       <c r="L3">
-        <v>1.7</v>
+        <v>0.78</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="O3">
-        <v>5612.3</v>
+        <v>9628.9636666666702</v>
       </c>
       <c r="P3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="T3" t="s">
         <v>57</v>
@@ -1525,25 +1513,22 @@
         <v>45</v>
       </c>
       <c r="Z3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE3" t="s">
         <v>48</v>
       </c>
-      <c r="AB3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE3" t="s">
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="s">
         <v>58</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>59</v>
       </c>
       <c r="AM3">
         <v>0</v>
@@ -1554,52 +1539,52 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4">
+        <v>841390</v>
+      </c>
+      <c r="E4">
+        <v>841385</v>
+      </c>
+      <c r="F4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" t="s">
         <v>60</v>
       </c>
-      <c r="C4" t="s">
+      <c r="H4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" t="s">
         <v>61</v>
       </c>
-      <c r="D4">
-        <v>861895</v>
-      </c>
-      <c r="E4">
-        <v>861892</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="J4" s="1">
+        <v>45930</v>
+      </c>
+      <c r="K4" s="1">
+        <v>45930</v>
+      </c>
+      <c r="L4">
+        <v>0.66</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>36</v>
+      </c>
+      <c r="O4">
+        <v>10305.593000000001</v>
+      </c>
+      <c r="P4" t="s">
+        <v>56</v>
+      </c>
+      <c r="T4" t="s">
         <v>62</v>
-      </c>
-      <c r="G4" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="1">
-        <v>45991</v>
-      </c>
-      <c r="K4" s="1">
-        <v>45991</v>
-      </c>
-      <c r="L4">
-        <v>1.33</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>42</v>
-      </c>
-      <c r="O4">
-        <v>3385.31116666667</v>
-      </c>
-      <c r="P4" t="s">
-        <v>66</v>
-      </c>
-      <c r="T4" t="s">
-        <v>67</v>
       </c>
       <c r="W4" t="s">
         <v>47</v>
@@ -1608,10 +1593,10 @@
         <v>45</v>
       </c>
       <c r="Z4" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1623,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="AM4">
         <v>0</v>
@@ -1634,52 +1619,52 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <v>862151</v>
+        <v>841399</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>841394</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="1">
+        <v>45930</v>
+      </c>
+      <c r="K5" s="1">
+        <v>45930</v>
+      </c>
+      <c r="L5">
+        <v>0.64</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5">
         <v>72</v>
       </c>
-      <c r="H5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" s="1">
-        <v>46002</v>
-      </c>
-      <c r="K5" s="1">
-        <v>46002</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>11</v>
-      </c>
       <c r="O5">
-        <v>20274</v>
+        <v>10309.163333333299</v>
       </c>
       <c r="P5" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="T5" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="W5" t="s">
         <v>47</v>
@@ -1688,25 +1673,22 @@
         <v>45</v>
       </c>
       <c r="Z5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE5" t="s">
         <v>48</v>
       </c>
-      <c r="AB5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE5" t="s">
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="s">
         <v>58</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>51</v>
       </c>
       <c r="AM5">
         <v>0</v>
@@ -1717,52 +1699,52 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>864636</v>
+        <v>863659</v>
       </c>
       <c r="E6">
-        <v>864627</v>
+        <v>863658</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H6" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I6" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="J6" s="1">
-        <v>46067</v>
+        <v>45973</v>
       </c>
       <c r="K6" s="1">
-        <v>46067</v>
+        <v>45973</v>
       </c>
       <c r="L6">
-        <v>1.55</v>
+        <v>0.68</v>
       </c>
       <c r="M6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="O6">
-        <v>923.97087499999998</v>
+        <v>1183.3530000000001</v>
       </c>
       <c r="P6" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T6" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="W6" t="s">
         <v>47</v>
@@ -1771,10 +1753,10 @@
         <v>45</v>
       </c>
       <c r="Z6" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1786,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM6">
         <v>0</v>
@@ -1797,37 +1779,37 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D7">
-        <v>864701</v>
+        <v>863668</v>
       </c>
       <c r="E7">
-        <v>864700</v>
+        <v>863667</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G7" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="J7" s="1">
-        <v>46067</v>
+        <v>45973</v>
       </c>
       <c r="K7" s="1">
-        <v>46067</v>
+        <v>45973</v>
       </c>
       <c r="L7">
-        <v>1.4</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
@@ -1836,13 +1818,13 @@
         <v>6</v>
       </c>
       <c r="O7">
-        <v>1349.0971875</v>
+        <v>1137.5975000000001</v>
       </c>
       <c r="P7" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T7" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="W7" t="s">
         <v>47</v>
@@ -1851,10 +1833,10 @@
         <v>45</v>
       </c>
       <c r="Z7" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF7">
         <v>0</v>
@@ -1866,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="AL7" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM7">
         <v>0</v>
@@ -1877,52 +1859,52 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8">
+        <v>863672</v>
+      </c>
+      <c r="E8">
+        <v>863667</v>
+      </c>
+      <c r="F8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" t="s">
         <v>77</v>
       </c>
-      <c r="D8">
-        <v>864717</v>
-      </c>
-      <c r="E8">
-        <v>864709</v>
-      </c>
-      <c r="F8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G8" t="s">
-        <v>90</v>
-      </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="I8" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="J8" s="1">
-        <v>46067</v>
+        <v>45973</v>
       </c>
       <c r="K8" s="1">
-        <v>46067</v>
+        <v>45973</v>
       </c>
       <c r="L8">
-        <v>1.38</v>
+        <v>0.52</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
       </c>
       <c r="N8">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="O8">
-        <v>1368.1051875000001</v>
+        <v>1168.63700666667</v>
       </c>
       <c r="P8" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T8" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="W8" t="s">
         <v>47</v>
@@ -1931,10 +1913,10 @@
         <v>45</v>
       </c>
       <c r="Z8" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF8">
         <v>0</v>
@@ -1946,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="AL8" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM8">
         <v>0</v>
@@ -1957,52 +1939,52 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>864964</v>
+        <v>863677</v>
       </c>
       <c r="E9">
-        <v>864960</v>
+        <v>863676</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I9" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="J9" s="1">
-        <v>46038</v>
+        <v>45973</v>
       </c>
       <c r="K9" s="1">
-        <v>46038</v>
+        <v>45973</v>
       </c>
       <c r="L9">
-        <v>1.53</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>1366.8395625000001</v>
+        <v>1106.7</v>
       </c>
       <c r="P9" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T9" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="W9" t="s">
         <v>47</v>
@@ -2011,10 +1993,10 @@
         <v>45</v>
       </c>
       <c r="Z9" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -2026,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="AL9" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM9">
         <v>0</v>
@@ -2037,52 +2019,52 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D10">
-        <v>865002</v>
+        <v>863681</v>
       </c>
       <c r="E10">
-        <v>865001</v>
+        <v>863676</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="I10" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="J10" s="1">
-        <v>46038</v>
+        <v>45973</v>
       </c>
       <c r="K10" s="1">
-        <v>46038</v>
+        <v>45973</v>
       </c>
       <c r="L10">
-        <v>2.13</v>
+        <v>0.62</v>
       </c>
       <c r="M10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="O10">
-        <v>1316.25</v>
+        <v>1147.5764999999999</v>
       </c>
       <c r="P10" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T10" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="W10" t="s">
         <v>47</v>
@@ -2091,10 +2073,10 @@
         <v>45</v>
       </c>
       <c r="Z10" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF10">
         <v>0</v>
@@ -2106,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="AL10" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM10">
         <v>0</v>
@@ -2117,37 +2099,37 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D11">
-        <v>865257</v>
+        <v>863685</v>
       </c>
       <c r="E11">
-        <v>865253</v>
+        <v>863676</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G11" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H11" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I11" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="J11" s="1">
-        <v>46017</v>
+        <v>45973</v>
       </c>
       <c r="K11" s="1">
-        <v>46017</v>
+        <v>45973</v>
       </c>
       <c r="L11">
-        <v>1.53</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M11" t="b">
         <v>0</v>
@@ -2156,13 +2138,13 @@
         <v>48</v>
       </c>
       <c r="O11">
-        <v>1147.5764999999999</v>
+        <v>1148.8515</v>
       </c>
       <c r="P11" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="W11" t="s">
         <v>47</v>
@@ -2171,10 +2153,10 @@
         <v>45</v>
       </c>
       <c r="Z11" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF11">
         <v>0</v>
@@ -2186,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM11">
         <v>0</v>
@@ -2197,52 +2179,52 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D12">
-        <v>865277</v>
+        <v>863689</v>
       </c>
       <c r="E12">
-        <v>865276</v>
+        <v>863676</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J12" s="1">
-        <v>46017</v>
+        <v>45973</v>
       </c>
       <c r="K12" s="1">
-        <v>46017</v>
+        <v>45973</v>
       </c>
       <c r="L12">
-        <v>1.55</v>
+        <v>0.42</v>
       </c>
       <c r="M12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="O12">
-        <v>1381.222125</v>
+        <v>1156.3485000000001</v>
       </c>
       <c r="P12" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T12" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="W12" t="s">
         <v>47</v>
@@ -2251,10 +2233,10 @@
         <v>45</v>
       </c>
       <c r="Z12" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF12">
         <v>0</v>
@@ -2266,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL12" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM12">
         <v>0</v>
@@ -2277,52 +2259,52 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D13">
-        <v>865306</v>
+        <v>864130</v>
       </c>
       <c r="E13">
-        <v>865294</v>
+        <v>864125</v>
       </c>
       <c r="F13" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="G13" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="H13" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="I13" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="J13" s="1">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c r="K13" s="1">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c r="L13">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="M13" t="b">
         <v>0</v>
       </c>
       <c r="N13">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>1377.2885624999999</v>
+        <v>1131.0136725</v>
       </c>
       <c r="P13" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T13" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="W13" t="s">
         <v>47</v>
@@ -2331,10 +2313,10 @@
         <v>45</v>
       </c>
       <c r="Z13" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF13">
         <v>0</v>
@@ -2346,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM13">
         <v>0</v>
@@ -2357,52 +2339,52 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14">
+        <v>864139</v>
+      </c>
+      <c r="E14">
+        <v>864134</v>
+      </c>
+      <c r="F14" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" t="s">
+        <v>97</v>
+      </c>
+      <c r="I14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J14" s="1">
+        <v>46022</v>
+      </c>
+      <c r="K14" s="1">
+        <v>46022</v>
+      </c>
+      <c r="L14">
+        <v>0.84</v>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>36</v>
+      </c>
+      <c r="O14">
+        <v>1201.5058837500001</v>
+      </c>
+      <c r="P14" t="s">
+        <v>56</v>
+      </c>
+      <c r="T14" t="s">
         <v>103</v>
-      </c>
-      <c r="C14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14">
-        <v>865310</v>
-      </c>
-      <c r="E14">
-        <v>865294</v>
-      </c>
-      <c r="F14" t="s">
-        <v>108</v>
-      </c>
-      <c r="G14" t="s">
-        <v>109</v>
-      </c>
-      <c r="H14" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" t="s">
-        <v>87</v>
-      </c>
-      <c r="J14" s="1">
-        <v>46017</v>
-      </c>
-      <c r="K14" s="1">
-        <v>46017</v>
-      </c>
-      <c r="L14">
-        <v>1.5</v>
-      </c>
-      <c r="M14" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>96</v>
-      </c>
-      <c r="O14">
-        <v>1403.0946562500001</v>
-      </c>
-      <c r="P14" t="s">
-        <v>66</v>
-      </c>
-      <c r="T14" t="s">
-        <v>110</v>
       </c>
       <c r="W14" t="s">
         <v>47</v>
@@ -2411,10 +2393,10 @@
         <v>45</v>
       </c>
       <c r="Z14" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF14">
         <v>0</v>
@@ -2426,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="AL14" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM14">
         <v>0</v>
@@ -2437,52 +2419,52 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D15">
-        <v>865542</v>
+        <v>864264</v>
       </c>
       <c r="E15">
-        <v>865541</v>
+        <v>864259</v>
       </c>
       <c r="F15" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="G15" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I15" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="J15" s="1">
-        <v>46001</v>
+        <v>45974</v>
       </c>
       <c r="K15" s="1">
-        <v>46001</v>
+        <v>45974</v>
       </c>
       <c r="L15">
-        <v>0.98</v>
+        <v>0.68</v>
       </c>
       <c r="M15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="O15">
-        <v>5458.2702192982497</v>
+        <v>4520.5761428571404</v>
       </c>
       <c r="P15" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T15" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="W15" t="s">
         <v>47</v>
@@ -2491,10 +2473,10 @@
         <v>45</v>
       </c>
       <c r="Z15" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE15" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="AF15">
         <v>0</v>
@@ -2506,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="AL15" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2517,52 +2499,52 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D16">
-        <v>865551</v>
+        <v>864268</v>
       </c>
       <c r="E16">
-        <v>865550</v>
+        <v>864259</v>
       </c>
       <c r="F16" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="G16" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="H16" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="I16" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="J16" s="1">
-        <v>46001</v>
+        <v>45974</v>
       </c>
       <c r="K16" s="1">
-        <v>46001</v>
+        <v>45974</v>
       </c>
       <c r="L16">
-        <v>1.43</v>
+        <v>0.64</v>
       </c>
       <c r="M16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="O16">
-        <v>5399.1421052631604</v>
+        <v>4520.5761428571404</v>
       </c>
       <c r="P16" t="s">
+        <v>56</v>
+      </c>
+      <c r="T16" t="s">
         <v>66</v>
-      </c>
-      <c r="T16" t="s">
-        <v>121</v>
       </c>
       <c r="W16" t="s">
         <v>47</v>
@@ -2571,10 +2553,10 @@
         <v>45</v>
       </c>
       <c r="Z16" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE16" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="AF16">
         <v>0</v>
@@ -2586,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="AL16" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="AM16">
         <v>0</v>
@@ -2597,52 +2579,52 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D17">
-        <v>865583</v>
+        <v>864272</v>
       </c>
       <c r="E17">
-        <v>865582</v>
+        <v>864259</v>
       </c>
       <c r="F17" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G17" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I17" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="J17" s="1">
-        <v>46001</v>
+        <v>45974</v>
       </c>
       <c r="K17" s="1">
-        <v>46001</v>
+        <v>45974</v>
       </c>
       <c r="L17">
-        <v>0.98</v>
+        <v>0.48</v>
       </c>
       <c r="M17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="O17">
-        <v>4370.9653947368397</v>
+        <v>4555.1481428571396</v>
       </c>
       <c r="P17" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="W17" t="s">
         <v>47</v>
@@ -2651,10 +2633,10 @@
         <v>45</v>
       </c>
       <c r="Z17" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE17" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="AF17">
         <v>0</v>
@@ -2666,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="AL17" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="AM17">
         <v>0</v>
@@ -2677,52 +2659,52 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D18">
-        <v>866496</v>
+        <v>864288</v>
       </c>
       <c r="E18">
-        <v>866495</v>
+        <v>864283</v>
       </c>
       <c r="F18" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="G18" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I18" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="J18" s="1">
-        <v>46022</v>
+        <v>45974</v>
       </c>
       <c r="K18" s="1">
-        <v>46022</v>
+        <v>45974</v>
       </c>
       <c r="L18">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="M18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>5420.625</v>
+        <v>2152.1318660833299</v>
       </c>
       <c r="P18" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T18" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="W18" t="s">
         <v>47</v>
@@ -2731,10 +2713,10 @@
         <v>45</v>
       </c>
       <c r="Z18" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF18">
         <v>0</v>
@@ -2746,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="AL18" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="AM18">
         <v>0</v>
@@ -2757,52 +2739,52 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D19">
-        <v>866835</v>
+        <v>865047</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>865042</v>
       </c>
       <c r="F19" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="G19" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="H19" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="I19" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="J19" s="1">
-        <v>46022</v>
+        <v>46038</v>
       </c>
       <c r="K19" s="1">
-        <v>46022</v>
+        <v>46038</v>
       </c>
       <c r="L19">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="M19" t="b">
         <v>0</v>
       </c>
       <c r="N19">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="O19">
-        <v>8447.7000000000007</v>
+        <v>1366.92996428571</v>
       </c>
       <c r="P19" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="T19" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="W19" t="s">
         <v>47</v>
@@ -2811,14 +2793,11 @@
         <v>45</v>
       </c>
       <c r="Z19" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE19" t="s">
         <v>48</v>
       </c>
-      <c r="AB19" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>50</v>
-      </c>
       <c r="AF19">
         <v>0</v>
       </c>
@@ -2829,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="AL19" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="AM19">
         <v>0</v>
@@ -2840,52 +2819,52 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="D20">
-        <v>868554</v>
+        <v>865567</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>865550</v>
       </c>
       <c r="F20" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="G20" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="I20" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="J20" s="1">
-        <v>46022</v>
+        <v>46001</v>
       </c>
       <c r="K20" s="1">
-        <v>46022</v>
+        <v>46001</v>
       </c>
       <c r="L20">
-        <v>1.7</v>
+        <v>1.23</v>
       </c>
       <c r="M20" t="b">
         <v>0</v>
       </c>
       <c r="N20">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="O20">
-        <v>5612.3</v>
+        <v>5774.3493609022598</v>
       </c>
       <c r="P20" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="T20" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="W20" t="s">
         <v>47</v>
@@ -2894,13 +2873,10 @@
         <v>45</v>
       </c>
       <c r="Z20" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="AE20" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF20">
         <v>0</v>
@@ -2912,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="AL20" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="AM20">
         <v>0</v>
@@ -2923,52 +2899,52 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D21">
-        <v>869261</v>
+        <v>867972</v>
       </c>
       <c r="E21">
-        <v>869260</v>
+        <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="G21" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="I21" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="J21" s="1">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="K21" s="1">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="L21">
-        <v>0.57999999999999996</v>
+        <v>2.6</v>
       </c>
       <c r="M21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O21">
-        <v>3297.7476388888899</v>
+        <v>5998.5</v>
       </c>
       <c r="P21" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="T21" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="W21" t="s">
         <v>47</v>
@@ -2977,10 +2953,13 @@
         <v>45</v>
       </c>
       <c r="Z21" t="s">
-        <v>66</v>
+        <v>129</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>130</v>
       </c>
       <c r="AE21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF21">
         <v>0</v>
@@ -2992,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="AL21" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="AM21">
         <v>0</v>
@@ -3003,37 +2982,37 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C22" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="D22">
-        <v>869270</v>
+        <v>868353</v>
       </c>
       <c r="E22">
-        <v>869269</v>
+        <v>868352</v>
       </c>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="G22" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H22" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="I22" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="J22" s="1">
-        <v>46015</v>
+        <v>45985</v>
       </c>
       <c r="K22" s="1">
-        <v>46015</v>
+        <v>45985</v>
       </c>
       <c r="L22">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="M22" t="b">
         <v>1</v>
@@ -3042,13 +3021,13 @@
         <v>6</v>
       </c>
       <c r="O22">
-        <v>3245.7833333333301</v>
+        <v>2242.1121250000001</v>
       </c>
       <c r="P22" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T22" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="W22" t="s">
         <v>47</v>
@@ -3057,10 +3036,10 @@
         <v>45</v>
       </c>
       <c r="Z22" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -3072,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="AL22" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM22">
         <v>0</v>
@@ -3083,52 +3062,52 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="C23" t="s">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="D23">
-        <v>870932</v>
+        <v>868362</v>
       </c>
       <c r="E23">
-        <v>870923</v>
+        <v>868361</v>
       </c>
       <c r="F23" t="s">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="G23" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="H23" t="s">
-        <v>150</v>
+        <v>97</v>
       </c>
       <c r="I23" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="J23" s="1">
-        <v>46008</v>
+        <v>45985</v>
       </c>
       <c r="K23" s="1">
-        <v>46008</v>
+        <v>45985</v>
       </c>
       <c r="L23">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="M23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="O23">
-        <v>1178.7869333333299</v>
+        <v>2229.5968750000002</v>
       </c>
       <c r="P23" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T23" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="W23" t="s">
         <v>47</v>
@@ -3137,10 +3116,10 @@
         <v>45</v>
       </c>
       <c r="Z23" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE23" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF23">
         <v>0</v>
@@ -3152,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="AL23" t="s">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="AM23">
         <v>0</v>
@@ -3163,52 +3142,52 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="C24" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="D24">
-        <v>870964</v>
+        <v>868366</v>
       </c>
       <c r="E24">
-        <v>870963</v>
+        <v>868361</v>
       </c>
       <c r="F24" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="G24" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="H24" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="I24" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="J24" s="1">
-        <v>46022</v>
+        <v>45985</v>
       </c>
       <c r="K24" s="1">
-        <v>46022</v>
+        <v>45985</v>
       </c>
       <c r="L24">
-        <v>3.35</v>
+        <v>0.9</v>
       </c>
       <c r="M24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="O24">
-        <v>730.55769230769204</v>
+        <v>2331.6758666666701</v>
       </c>
       <c r="P24" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T24" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="W24" t="s">
         <v>47</v>
@@ -3217,10 +3196,10 @@
         <v>45</v>
       </c>
       <c r="Z24" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE24" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="AF24">
         <v>0</v>
@@ -3232,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="AL24" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM24">
         <v>0</v>
@@ -3243,28 +3222,28 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
-        <v>161</v>
+        <v>94</v>
       </c>
       <c r="D25">
-        <v>871265</v>
+        <v>872491</v>
       </c>
       <c r="E25">
-        <v>871264</v>
+        <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="G25" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="H25" t="s">
-        <v>164</v>
+        <v>126</v>
       </c>
       <c r="I25" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="J25" s="1">
         <v>46022</v>
@@ -3273,22 +3252,22 @@
         <v>46022</v>
       </c>
       <c r="L25">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="M25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>1664.52342519685</v>
+        <v>5631.8</v>
       </c>
       <c r="P25" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="T25" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="W25" t="s">
         <v>47</v>
@@ -3297,10 +3276,13 @@
         <v>45</v>
       </c>
       <c r="Z25" t="s">
-        <v>66</v>
+        <v>129</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>130</v>
       </c>
       <c r="AE25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF25">
         <v>0</v>
@@ -3312,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="AL25" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AM25">
         <v>0</v>
@@ -3323,28 +3305,28 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="C26" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="D26">
-        <v>871275</v>
+        <v>873095</v>
       </c>
       <c r="E26">
-        <v>871264</v>
+        <v>873086</v>
       </c>
       <c r="F26" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="G26" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="H26" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="I26" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="J26" s="1">
         <v>46022</v>
@@ -3353,22 +3335,22 @@
         <v>46022</v>
       </c>
       <c r="L26">
-        <v>0.98</v>
+        <v>1.75</v>
       </c>
       <c r="M26" t="b">
         <v>0</v>
       </c>
       <c r="N26">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="O26">
-        <v>1744.48525646794</v>
+        <v>6822.8757638888901</v>
       </c>
       <c r="P26" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T26" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="W26" t="s">
         <v>47</v>
@@ -3377,10 +3359,10 @@
         <v>45</v>
       </c>
       <c r="Z26" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE26" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF26">
         <v>0</v>
@@ -3392,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="AL26" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="AM26">
         <v>0</v>
@@ -3403,52 +3385,52 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="C27" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="D27">
-        <v>871383</v>
+        <v>874027</v>
       </c>
       <c r="E27">
-        <v>871378</v>
+        <v>874022</v>
       </c>
       <c r="F27" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="G27" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="H27" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="I27" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J27" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="K27" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="L27">
-        <v>0.82</v>
+        <v>0.94</v>
       </c>
       <c r="M27" t="b">
         <v>0</v>
       </c>
       <c r="N27">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="O27">
-        <v>1786.48429645123</v>
+        <v>3372.9685154214599</v>
       </c>
       <c r="P27" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T27" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="W27" t="s">
         <v>47</v>
@@ -3457,10 +3439,10 @@
         <v>45</v>
       </c>
       <c r="Z27" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF27">
         <v>0</v>
@@ -3472,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="AL27" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AM27">
         <v>0</v>
@@ -3483,52 +3465,52 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="C28" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="D28">
-        <v>871907</v>
+        <v>874049</v>
       </c>
       <c r="E28">
-        <v>871894</v>
+        <v>874044</v>
       </c>
       <c r="F28" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G28" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="H28" t="s">
-        <v>150</v>
+        <v>97</v>
       </c>
       <c r="I28" t="s">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="J28" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="K28" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="L28">
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="M28" t="b">
         <v>0</v>
       </c>
       <c r="N28">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>1744.48525646794</v>
+        <v>1557.56608333333</v>
       </c>
       <c r="P28" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T28" t="s">
-        <v>175</v>
+        <v>99</v>
       </c>
       <c r="W28" t="s">
         <v>47</v>
@@ -3537,10 +3519,10 @@
         <v>45</v>
       </c>
       <c r="Z28" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF28">
         <v>0</v>
@@ -3552,7 +3534,7 @@
         <v>0</v>
       </c>
       <c r="AL28" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AM28">
         <v>0</v>
@@ -3563,52 +3545,52 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C29" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D29">
-        <v>871929</v>
+        <v>874127</v>
       </c>
       <c r="E29">
-        <v>871928</v>
+        <v>874110</v>
       </c>
       <c r="F29" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="G29" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="H29" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="I29" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="J29" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="K29" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="L29">
-        <v>0.72</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="M29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="O29">
-        <v>1700.8016811023599</v>
+        <v>4560.1875</v>
       </c>
       <c r="P29" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T29" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="W29" t="s">
         <v>47</v>
@@ -3617,10 +3599,10 @@
         <v>45</v>
       </c>
       <c r="Z29" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE29" t="s">
-        <v>50</v>
+        <v>166</v>
       </c>
       <c r="AF29">
         <v>0</v>
@@ -3632,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="AL29" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="AM29">
         <v>0</v>
@@ -3643,52 +3625,52 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30">
+        <v>877058</v>
+      </c>
+      <c r="E30">
+        <v>877053</v>
+      </c>
+      <c r="F30" t="s">
+        <v>169</v>
+      </c>
+      <c r="G30" t="s">
+        <v>170</v>
+      </c>
+      <c r="H30" t="s">
+        <v>78</v>
+      </c>
+      <c r="I30" t="s">
         <v>171</v>
       </c>
-      <c r="D30">
-        <v>871942</v>
-      </c>
-      <c r="E30">
-        <v>871937</v>
-      </c>
-      <c r="F30" t="s">
-        <v>180</v>
-      </c>
-      <c r="G30" t="s">
-        <v>181</v>
-      </c>
-      <c r="H30" t="s">
-        <v>119</v>
-      </c>
-      <c r="I30" t="s">
-        <v>179</v>
-      </c>
       <c r="J30" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="K30" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="L30">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="M30" t="b">
         <v>0</v>
       </c>
       <c r="N30">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="O30">
-        <v>1701.75874251968</v>
+        <v>2319.4021593749999</v>
       </c>
       <c r="P30" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T30" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="W30" t="s">
         <v>47</v>
@@ -3697,10 +3679,10 @@
         <v>45</v>
       </c>
       <c r="Z30" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE30" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF30">
         <v>0</v>
@@ -3712,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="AL30" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AM30">
         <v>0</v>
@@ -3723,52 +3705,52 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" t="s">
+        <v>173</v>
+      </c>
+      <c r="D31">
+        <v>877310</v>
+      </c>
+      <c r="E31">
+        <v>877293</v>
+      </c>
+      <c r="F31" t="s">
+        <v>174</v>
+      </c>
+      <c r="G31" t="s">
+        <v>175</v>
+      </c>
+      <c r="H31" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31" t="s">
         <v>176</v>
       </c>
-      <c r="C31" t="s">
-        <v>171</v>
-      </c>
-      <c r="D31">
-        <v>871946</v>
-      </c>
-      <c r="E31">
-        <v>871937</v>
-      </c>
-      <c r="F31" t="s">
-        <v>167</v>
-      </c>
-      <c r="G31" t="s">
-        <v>168</v>
-      </c>
-      <c r="H31" t="s">
-        <v>119</v>
-      </c>
-      <c r="I31" t="s">
-        <v>179</v>
-      </c>
       <c r="J31" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="K31" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="L31">
-        <v>0.82</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="b">
         <v>0</v>
       </c>
       <c r="N31">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="O31">
-        <v>1713.3397175196801</v>
+        <v>5282.30670516185</v>
       </c>
       <c r="P31" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T31" t="s">
-        <v>126</v>
+        <v>177</v>
       </c>
       <c r="W31" t="s">
         <v>47</v>
@@ -3777,10 +3759,10 @@
         <v>45</v>
       </c>
       <c r="Z31" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF31">
         <v>0</v>
@@ -3792,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="AL31" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AM31">
         <v>0</v>
@@ -3803,52 +3785,52 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C32" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D32">
-        <v>871950</v>
+        <v>877406</v>
       </c>
       <c r="E32">
-        <v>871937</v>
+        <v>877401</v>
       </c>
       <c r="F32" t="s">
+        <v>180</v>
+      </c>
+      <c r="G32" t="s">
+        <v>181</v>
+      </c>
+      <c r="H32" t="s">
+        <v>97</v>
+      </c>
+      <c r="I32" t="s">
+        <v>182</v>
+      </c>
+      <c r="J32" s="1">
+        <v>46053</v>
+      </c>
+      <c r="K32" s="1">
+        <v>46053</v>
+      </c>
+      <c r="L32">
+        <v>1.33</v>
+      </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>6</v>
+      </c>
+      <c r="O32">
+        <v>1678.7554724409399</v>
+      </c>
+      <c r="P32" t="s">
+        <v>56</v>
+      </c>
+      <c r="T32" t="s">
         <v>183</v>
-      </c>
-      <c r="G32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H32" t="s">
-        <v>119</v>
-      </c>
-      <c r="I32" t="s">
-        <v>141</v>
-      </c>
-      <c r="J32" s="1">
-        <v>46022</v>
-      </c>
-      <c r="K32" s="1">
-        <v>46022</v>
-      </c>
-      <c r="L32">
-        <v>0.64</v>
-      </c>
-      <c r="M32" t="b">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>30</v>
-      </c>
-      <c r="O32">
-        <v>1713.3397175196801</v>
-      </c>
-      <c r="P32" t="s">
-        <v>66</v>
-      </c>
-      <c r="T32" t="s">
-        <v>185</v>
       </c>
       <c r="W32" t="s">
         <v>47</v>
@@ -3857,10 +3839,10 @@
         <v>45</v>
       </c>
       <c r="Z32" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE32" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF32">
         <v>0</v>
@@ -3872,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="AL32" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AM32">
         <v>0</v>
@@ -3883,52 +3865,52 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33">
+        <v>877422</v>
+      </c>
+      <c r="E33">
+        <v>877419</v>
+      </c>
+      <c r="F33" t="s">
+        <v>184</v>
+      </c>
+      <c r="G33" t="s">
+        <v>185</v>
+      </c>
+      <c r="H33" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" t="s">
+        <v>182</v>
+      </c>
+      <c r="J33" s="1">
+        <v>46053</v>
+      </c>
+      <c r="K33" s="1">
+        <v>46053</v>
+      </c>
+      <c r="L33">
+        <v>1.35</v>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>42</v>
+      </c>
+      <c r="O33">
+        <v>1731.2498757030401</v>
+      </c>
+      <c r="P33" t="s">
+        <v>56</v>
+      </c>
+      <c r="T33" t="s">
         <v>186</v>
-      </c>
-      <c r="C33" t="s">
-        <v>171</v>
-      </c>
-      <c r="D33">
-        <v>871980</v>
-      </c>
-      <c r="E33">
-        <v>871974</v>
-      </c>
-      <c r="F33" t="s">
-        <v>187</v>
-      </c>
-      <c r="G33" t="s">
-        <v>188</v>
-      </c>
-      <c r="H33" t="s">
-        <v>64</v>
-      </c>
-      <c r="I33" t="s">
-        <v>100</v>
-      </c>
-      <c r="J33" s="1">
-        <v>46022</v>
-      </c>
-      <c r="K33" s="1">
-        <v>46022</v>
-      </c>
-      <c r="L33">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M33" t="b">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>48</v>
-      </c>
-      <c r="O33">
-        <v>584.45537081625696</v>
-      </c>
-      <c r="P33" t="s">
-        <v>66</v>
-      </c>
-      <c r="T33" t="s">
-        <v>189</v>
       </c>
       <c r="W33" t="s">
         <v>47</v>
@@ -3937,10 +3919,10 @@
         <v>45</v>
       </c>
       <c r="Z33" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE33" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -3952,7 +3934,7 @@
         <v>0</v>
       </c>
       <c r="AL33" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AM33">
         <v>0</v>
@@ -3963,52 +3945,52 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="C34" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D34">
-        <v>872046</v>
+        <v>877426</v>
       </c>
       <c r="E34">
-        <v>872045</v>
+        <v>877419</v>
       </c>
       <c r="F34" t="s">
-        <v>139</v>
+        <v>187</v>
       </c>
       <c r="G34" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="H34" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="I34" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="J34" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="K34" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="L34">
-        <v>0.57999999999999996</v>
+        <v>1.3</v>
       </c>
       <c r="M34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="O34">
-        <v>1700.8016811023599</v>
+        <v>1731.2498757030401</v>
       </c>
       <c r="P34" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T34" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="W34" t="s">
         <v>47</v>
@@ -4017,10 +3999,10 @@
         <v>45</v>
       </c>
       <c r="Z34" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE34" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF34">
         <v>0</v>
@@ -4032,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="AL34" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AM34">
         <v>0</v>
@@ -4043,37 +4025,37 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" t="s">
+        <v>173</v>
+      </c>
+      <c r="D35">
+        <v>877463</v>
+      </c>
+      <c r="E35">
+        <v>877459</v>
+      </c>
+      <c r="F35" t="s">
         <v>191</v>
       </c>
-      <c r="C35" t="s">
-        <v>171</v>
-      </c>
-      <c r="D35">
-        <v>872109</v>
-      </c>
-      <c r="E35">
-        <v>872094</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>192</v>
       </c>
-      <c r="G35" t="s">
-        <v>193</v>
-      </c>
       <c r="H35" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="I35" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="J35" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="K35" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="L35">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
@@ -4082,13 +4064,13 @@
         <v>84</v>
       </c>
       <c r="O35">
-        <v>1076.9989407361199</v>
+        <v>1730.88920563836</v>
       </c>
       <c r="P35" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T35" t="s">
-        <v>194</v>
+        <v>46</v>
       </c>
       <c r="W35" t="s">
         <v>47</v>
@@ -4097,10 +4079,10 @@
         <v>45</v>
       </c>
       <c r="Z35" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE35" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF35">
         <v>0</v>
@@ -4112,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="AL35" t="s">
-        <v>68</v>
+        <v>156</v>
       </c>
       <c r="AM35">
         <v>0</v>
@@ -4123,52 +4105,52 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
+        <v>190</v>
+      </c>
+      <c r="C36" t="s">
+        <v>173</v>
+      </c>
+      <c r="D36">
+        <v>877467</v>
+      </c>
+      <c r="E36">
+        <v>877459</v>
+      </c>
+      <c r="F36" t="s">
+        <v>193</v>
+      </c>
+      <c r="G36" t="s">
+        <v>194</v>
+      </c>
+      <c r="H36" t="s">
+        <v>97</v>
+      </c>
+      <c r="I36" t="s">
         <v>195</v>
       </c>
-      <c r="C36" t="s">
-        <v>171</v>
-      </c>
-      <c r="D36">
-        <v>872131</v>
-      </c>
-      <c r="E36">
-        <v>872130</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="J36" s="1">
+        <v>46053</v>
+      </c>
+      <c r="K36" s="1">
+        <v>46053</v>
+      </c>
+      <c r="L36">
+        <v>1.45</v>
+      </c>
+      <c r="M36" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>84</v>
+      </c>
+      <c r="O36">
+        <v>1730.88920563836</v>
+      </c>
+      <c r="P36" t="s">
+        <v>56</v>
+      </c>
+      <c r="T36" t="s">
         <v>196</v>
-      </c>
-      <c r="G36" t="s">
-        <v>197</v>
-      </c>
-      <c r="H36" t="s">
-        <v>164</v>
-      </c>
-      <c r="I36" t="s">
-        <v>100</v>
-      </c>
-      <c r="J36" s="1">
-        <v>46022</v>
-      </c>
-      <c r="K36" s="1">
-        <v>46022</v>
-      </c>
-      <c r="L36">
-        <v>2.25</v>
-      </c>
-      <c r="M36" t="b">
-        <v>1</v>
-      </c>
-      <c r="N36">
-        <v>6</v>
-      </c>
-      <c r="O36">
-        <v>524.28668122270699</v>
-      </c>
-      <c r="P36" t="s">
-        <v>66</v>
-      </c>
-      <c r="T36" t="s">
-        <v>198</v>
       </c>
       <c r="W36" t="s">
         <v>47</v>
@@ -4177,10 +4159,10 @@
         <v>45</v>
       </c>
       <c r="Z36" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE36" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF36">
         <v>0</v>
@@ -4192,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="AL36" t="s">
-        <v>68</v>
+        <v>156</v>
       </c>
       <c r="AM36">
         <v>0</v>
@@ -4203,52 +4185,52 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C37" t="s">
-        <v>171</v>
+        <v>51</v>
       </c>
       <c r="D37">
-        <v>872139</v>
+        <v>877490</v>
       </c>
       <c r="E37">
-        <v>872130</v>
+        <v>877482</v>
       </c>
       <c r="F37" t="s">
+        <v>198</v>
+      </c>
+      <c r="G37" t="s">
         <v>199</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" t="s">
         <v>200</v>
       </c>
-      <c r="H37" t="s">
-        <v>64</v>
-      </c>
-      <c r="I37" t="s">
+      <c r="J37" s="1">
+        <v>46053</v>
+      </c>
+      <c r="K37" s="1">
+        <v>46053</v>
+      </c>
+      <c r="L37">
+        <v>1.65</v>
+      </c>
+      <c r="M37" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>27</v>
+      </c>
+      <c r="O37">
+        <v>1184.85252033406</v>
+      </c>
+      <c r="P37" t="s">
+        <v>56</v>
+      </c>
+      <c r="T37" t="s">
         <v>201</v>
-      </c>
-      <c r="J37" s="1">
-        <v>46022</v>
-      </c>
-      <c r="K37" s="1">
-        <v>46022</v>
-      </c>
-      <c r="L37">
-        <v>1.18</v>
-      </c>
-      <c r="M37" t="b">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>42</v>
-      </c>
-      <c r="O37">
-        <v>542.34338220004202</v>
-      </c>
-      <c r="P37" t="s">
-        <v>66</v>
-      </c>
-      <c r="T37" t="s">
-        <v>202</v>
       </c>
       <c r="W37" t="s">
         <v>47</v>
@@ -4257,10 +4239,10 @@
         <v>45</v>
       </c>
       <c r="Z37" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE37" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF37">
         <v>0</v>
@@ -4272,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="AL37" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="AM37">
         <v>0</v>
@@ -4283,52 +4265,52 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C38" t="s">
-        <v>171</v>
+        <v>51</v>
       </c>
       <c r="D38">
-        <v>872143</v>
+        <v>877495</v>
       </c>
       <c r="E38">
-        <v>872130</v>
+        <v>877494</v>
       </c>
       <c r="F38" t="s">
+        <v>202</v>
+      </c>
+      <c r="G38" t="s">
         <v>203</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I38" t="s">
+        <v>44</v>
+      </c>
+      <c r="J38" s="1">
+        <v>46053</v>
+      </c>
+      <c r="K38" s="1">
+        <v>46053</v>
+      </c>
+      <c r="L38">
+        <v>1.43</v>
+      </c>
+      <c r="M38" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38">
+        <v>18</v>
+      </c>
+      <c r="O38">
+        <v>1190.7252614379099</v>
+      </c>
+      <c r="P38" t="s">
+        <v>56</v>
+      </c>
+      <c r="T38" t="s">
         <v>204</v>
-      </c>
-      <c r="H38" t="s">
-        <v>64</v>
-      </c>
-      <c r="I38" t="s">
-        <v>80</v>
-      </c>
-      <c r="J38" s="1">
-        <v>46022</v>
-      </c>
-      <c r="K38" s="1">
-        <v>46022</v>
-      </c>
-      <c r="L38">
-        <v>1.88</v>
-      </c>
-      <c r="M38" t="b">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>84</v>
-      </c>
-      <c r="O38">
-        <v>550.19223861509704</v>
-      </c>
-      <c r="P38" t="s">
-        <v>66</v>
-      </c>
-      <c r="T38" t="s">
-        <v>205</v>
       </c>
       <c r="W38" t="s">
         <v>47</v>
@@ -4337,10 +4319,10 @@
         <v>45</v>
       </c>
       <c r="Z38" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE38" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF38">
         <v>0</v>
@@ -4352,7 +4334,7 @@
         <v>0</v>
       </c>
       <c r="AL38" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="AM38">
         <v>0</v>
@@ -4363,52 +4345,52 @@
         <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C39" t="s">
-        <v>171</v>
+        <v>51</v>
       </c>
       <c r="D39">
-        <v>872150</v>
+        <v>877531</v>
       </c>
       <c r="E39">
-        <v>872149</v>
+        <v>877523</v>
       </c>
       <c r="F39" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="G39" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="H39" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="I39" t="s">
-        <v>87</v>
+        <v>200</v>
       </c>
       <c r="J39" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="K39" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="L39">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="M39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="O39">
-        <v>1621.0756154855601</v>
+        <v>1184.85252033406</v>
       </c>
       <c r="P39" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T39" t="s">
-        <v>91</v>
+        <v>201</v>
       </c>
       <c r="W39" t="s">
         <v>47</v>
@@ -4417,10 +4399,10 @@
         <v>45</v>
       </c>
       <c r="Z39" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE39" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF39">
         <v>0</v>
@@ -4432,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="AL39" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM39">
         <v>0</v>
@@ -4443,52 +4425,52 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
+        <v>205</v>
+      </c>
+      <c r="C40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40">
+        <v>877540</v>
+      </c>
+      <c r="E40">
+        <v>877535</v>
+      </c>
+      <c r="F40" t="s">
+        <v>206</v>
+      </c>
+      <c r="G40" t="s">
         <v>207</v>
       </c>
-      <c r="C40" t="s">
+      <c r="H40" t="s">
+        <v>97</v>
+      </c>
+      <c r="I40" t="s">
         <v>208</v>
       </c>
-      <c r="D40">
-        <v>872346</v>
-      </c>
-      <c r="E40">
-        <v>872341</v>
-      </c>
-      <c r="F40" t="s">
-        <v>209</v>
-      </c>
-      <c r="G40" t="s">
-        <v>210</v>
-      </c>
-      <c r="H40" t="s">
-        <v>150</v>
-      </c>
-      <c r="I40" t="s">
-        <v>211</v>
-      </c>
       <c r="J40" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="K40" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="L40">
-        <v>0.56000000000000005</v>
+        <v>0.84</v>
       </c>
       <c r="M40" t="b">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>216</v>
+        <v>144</v>
       </c>
       <c r="O40">
-        <v>4554.6230290277799</v>
+        <v>1240.8002235838801</v>
       </c>
       <c r="P40" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T40" t="s">
-        <v>212</v>
+        <v>103</v>
       </c>
       <c r="W40" t="s">
         <v>47</v>
@@ -4497,10 +4479,10 @@
         <v>45</v>
       </c>
       <c r="Z40" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE40" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF40">
         <v>0</v>
@@ -4512,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="AL40" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="AM40">
         <v>0</v>
@@ -4523,52 +4505,52 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C41" t="s">
-        <v>208</v>
+        <v>51</v>
       </c>
       <c r="D41">
-        <v>872359</v>
+        <v>877555</v>
       </c>
       <c r="E41">
-        <v>872350</v>
+        <v>877548</v>
       </c>
       <c r="F41" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G41" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H41" t="s">
-        <v>150</v>
+        <v>97</v>
       </c>
       <c r="I41" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="J41" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="K41" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="L41">
-        <v>0.66</v>
+        <v>1.65</v>
       </c>
       <c r="M41" t="b">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="O41">
-        <v>4472.92</v>
+        <v>1235.27893510738</v>
       </c>
       <c r="P41" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T41" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="W41" t="s">
         <v>47</v>
@@ -4577,10 +4559,10 @@
         <v>45</v>
       </c>
       <c r="Z41" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE41" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF41">
         <v>0</v>
@@ -4592,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="AL41" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="AM41">
         <v>0</v>
@@ -4603,52 +4585,52 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C42" t="s">
-        <v>208</v>
+        <v>51</v>
       </c>
       <c r="D42">
-        <v>872363</v>
+        <v>877576</v>
       </c>
       <c r="E42">
-        <v>872350</v>
+        <v>877575</v>
       </c>
       <c r="F42" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="G42" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="H42" t="s">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="I42" t="s">
-        <v>219</v>
+        <v>44</v>
       </c>
       <c r="J42" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="K42" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="L42">
-        <v>0.52</v>
+        <v>1.43</v>
       </c>
       <c r="M42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42">
-        <v>180</v>
+        <v>6</v>
       </c>
       <c r="O42">
-        <v>4472.92</v>
+        <v>880.09840277777801</v>
       </c>
       <c r="P42" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T42" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="W42" t="s">
         <v>47</v>
@@ -4657,10 +4639,10 @@
         <v>45</v>
       </c>
       <c r="Z42" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE42" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF42">
         <v>0</v>
@@ -4672,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="AL42" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="AM42">
         <v>0</v>
@@ -4683,52 +4665,52 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C43" t="s">
-        <v>208</v>
+        <v>51</v>
       </c>
       <c r="D43">
-        <v>872367</v>
+        <v>877616</v>
       </c>
       <c r="E43">
-        <v>872350</v>
+        <v>877615</v>
       </c>
       <c r="F43" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="G43" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="H43" t="s">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="I43" t="s">
-        <v>223</v>
+        <v>44</v>
       </c>
       <c r="J43" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="K43" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="L43">
-        <v>0.94</v>
+        <v>1.43</v>
       </c>
       <c r="M43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43">
-        <v>360</v>
+        <v>6</v>
       </c>
       <c r="O43">
-        <v>4559.5174999999999</v>
+        <v>880.09840277777801</v>
       </c>
       <c r="P43" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T43" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="W43" t="s">
         <v>47</v>
@@ -4737,10 +4719,10 @@
         <v>45</v>
       </c>
       <c r="Z43" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE43" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF43">
         <v>0</v>
@@ -4752,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="AL43" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="AM43">
         <v>0</v>
@@ -4763,52 +4745,52 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="C44" t="s">
-        <v>208</v>
+        <v>51</v>
       </c>
       <c r="D44">
-        <v>872410</v>
+        <v>877635</v>
       </c>
       <c r="E44">
-        <v>872393</v>
+        <v>877628</v>
       </c>
       <c r="F44" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="G44" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="H44" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="I44" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="J44" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="K44" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="L44">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
       </c>
       <c r="N44">
-        <v>300</v>
+        <v>42</v>
       </c>
       <c r="O44">
-        <v>4559.5844999999999</v>
+        <v>895.89323015873003</v>
       </c>
       <c r="P44" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T44" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="W44" t="s">
         <v>47</v>
@@ -4817,10 +4799,10 @@
         <v>45</v>
       </c>
       <c r="Z44" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE44" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF44">
         <v>0</v>
@@ -4832,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="AL44" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="AM44">
         <v>0</v>
@@ -4843,52 +4825,52 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="C45" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D45">
-        <v>872750</v>
+        <v>877659</v>
       </c>
       <c r="E45">
-        <v>872749</v>
+        <v>877655</v>
       </c>
       <c r="F45" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="G45" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="H45" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="I45" t="s">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="J45" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="K45" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="L45">
-        <v>2.2799999999999998</v>
+        <v>1</v>
       </c>
       <c r="M45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="O45">
-        <v>2703.1715686274501</v>
+        <v>4452.26166666667</v>
       </c>
       <c r="P45" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T45" t="s">
-        <v>234</v>
+        <v>99</v>
       </c>
       <c r="W45" t="s">
         <v>47</v>
@@ -4897,10 +4879,10 @@
         <v>45</v>
       </c>
       <c r="Z45" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE45" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="AF45">
         <v>0</v>
@@ -4912,7 +4894,7 @@
         <v>0</v>
       </c>
       <c r="AL45" t="s">
-        <v>235</v>
+        <v>58</v>
       </c>
       <c r="AM45">
         <v>0</v>
@@ -4923,52 +4905,52 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="C46" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D46">
-        <v>872773</v>
+        <v>877717</v>
       </c>
       <c r="E46">
-        <v>872764</v>
+        <v>877712</v>
       </c>
       <c r="F46" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="G46" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="H46" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I46" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="J46" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="K46" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="L46">
-        <v>1.75</v>
+        <v>0.98</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
       </c>
       <c r="N46">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="O46">
-        <v>4673.23975743349</v>
+        <v>2185.1071395833301</v>
       </c>
       <c r="P46" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T46" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="W46" t="s">
         <v>47</v>
@@ -4977,10 +4959,10 @@
         <v>45</v>
       </c>
       <c r="Z46" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE46" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="AF46">
         <v>0</v>
@@ -4992,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="AL46" t="s">
-        <v>235</v>
+        <v>58</v>
       </c>
       <c r="AM46">
         <v>0</v>
@@ -5003,37 +4985,37 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="C47" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D47">
-        <v>872810</v>
+        <v>877722</v>
       </c>
       <c r="E47">
-        <v>872809</v>
+        <v>877721</v>
       </c>
       <c r="F47" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="G47" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="H47" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I47" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="J47" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="K47" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="L47">
-        <v>1.7</v>
+        <v>0.94</v>
       </c>
       <c r="M47" t="b">
         <v>1</v>
@@ -5042,13 +5024,13 @@
         <v>6</v>
       </c>
       <c r="O47">
-        <v>2176.1999999999998</v>
+        <v>2217.5494791666702</v>
       </c>
       <c r="P47" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T47" t="s">
-        <v>57</v>
+        <v>155</v>
       </c>
       <c r="W47" t="s">
         <v>47</v>
@@ -5057,10 +5039,10 @@
         <v>45</v>
       </c>
       <c r="Z47" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE47" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="AF47">
         <v>0</v>
@@ -5072,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="AL47" t="s">
-        <v>235</v>
+        <v>58</v>
       </c>
       <c r="AM47">
         <v>0</v>
@@ -5083,52 +5065,52 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C48" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D48">
-        <v>872826</v>
+        <v>877734</v>
       </c>
       <c r="E48">
-        <v>872825</v>
+        <v>877730</v>
       </c>
       <c r="F48" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="G48" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="H48" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="I48" t="s">
-        <v>120</v>
+        <v>227</v>
       </c>
       <c r="J48" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="K48" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="L48">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="M48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="O48">
-        <v>5406.54</v>
+        <v>2232.2281944444399</v>
       </c>
       <c r="P48" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T48" t="s">
-        <v>88</v>
+        <v>228</v>
       </c>
       <c r="W48" t="s">
         <v>47</v>
@@ -5137,10 +5119,10 @@
         <v>45</v>
       </c>
       <c r="Z48" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE48" t="s">
-        <v>247</v>
+        <v>166</v>
       </c>
       <c r="AF48">
         <v>0</v>
@@ -5152,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AL48" t="s">
-        <v>235</v>
+        <v>58</v>
       </c>
       <c r="AM48">
         <v>0</v>
@@ -5163,52 +5145,52 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="C49" t="s">
+        <v>230</v>
+      </c>
+      <c r="D49">
+        <v>877943</v>
+      </c>
+      <c r="E49">
+        <v>877942</v>
+      </c>
+      <c r="F49" t="s">
         <v>231</v>
       </c>
-      <c r="D49">
-        <v>872854</v>
-      </c>
-      <c r="E49">
-        <v>872849</v>
-      </c>
-      <c r="F49" t="s">
-        <v>249</v>
-      </c>
       <c r="G49" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="H49" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I49" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="J49" s="1">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="K49" s="1">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="L49">
-        <v>1.05</v>
+        <v>0.98</v>
       </c>
       <c r="M49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="O49">
-        <v>6746.7</v>
+        <v>2268.5906249999998</v>
       </c>
       <c r="P49" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T49" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="W49" t="s">
         <v>47</v>
@@ -5217,10 +5199,10 @@
         <v>45</v>
       </c>
       <c r="Z49" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE49" t="s">
-        <v>247</v>
+        <v>120</v>
       </c>
       <c r="AF49">
         <v>0</v>
@@ -5232,7 +5214,7 @@
         <v>0</v>
       </c>
       <c r="AL49" t="s">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="AM49">
         <v>0</v>
@@ -5243,52 +5225,52 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="C50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D50">
-        <v>872888</v>
+        <v>877951</v>
       </c>
       <c r="E50">
-        <v>872887</v>
+        <v>877942</v>
       </c>
       <c r="F50" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="G50" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="H50" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I50" t="s">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="J50" s="1">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="K50" s="1">
-        <v>46022</v>
+        <v>46051</v>
       </c>
       <c r="L50">
-        <v>1.9</v>
+        <v>1.05</v>
       </c>
       <c r="M50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="O50">
-        <v>3241.125</v>
+        <v>2379.5717343749998</v>
       </c>
       <c r="P50" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T50" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="W50" t="s">
         <v>47</v>
@@ -5297,10 +5279,10 @@
         <v>45</v>
       </c>
       <c r="Z50" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE50" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AF50">
         <v>0</v>
@@ -5312,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="AL50" t="s">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="AM50">
         <v>0</v>
@@ -5323,37 +5305,37 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C51" t="s">
-        <v>231</v>
+        <v>161</v>
       </c>
       <c r="D51">
-        <v>872892</v>
+        <v>878085</v>
       </c>
       <c r="E51">
-        <v>872887</v>
+        <v>878080</v>
       </c>
       <c r="F51" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="G51" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="H51" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="I51" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="J51" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="K51" s="1">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="L51">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
@@ -5362,13 +5344,13 @@
         <v>54</v>
       </c>
       <c r="O51">
-        <v>3333.4197222222201</v>
+        <v>3677.18784511785</v>
       </c>
       <c r="P51" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T51" t="s">
-        <v>259</v>
+        <v>99</v>
       </c>
       <c r="W51" t="s">
         <v>47</v>
@@ -5377,10 +5359,10 @@
         <v>45</v>
       </c>
       <c r="Z51" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE51" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="AF51">
         <v>0</v>
@@ -5392,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="AL51" t="s">
-        <v>235</v>
+        <v>149</v>
       </c>
       <c r="AM51">
         <v>0</v>
@@ -5403,52 +5385,52 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="C52" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="D52">
-        <v>872910</v>
+        <v>878142</v>
       </c>
       <c r="E52">
-        <v>872901</v>
+        <v>878137</v>
       </c>
       <c r="F52" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="G52" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="H52" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I52" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="J52" s="1">
-        <v>46022</v>
+        <v>46054</v>
       </c>
       <c r="K52" s="1">
-        <v>46022</v>
+        <v>46054</v>
       </c>
       <c r="L52">
-        <v>1.6</v>
+        <v>0.76</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
       </c>
       <c r="N52">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="O52">
-        <v>2960.5841071428599</v>
+        <v>2183.9586231666699</v>
       </c>
       <c r="P52" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T52" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="W52" t="s">
         <v>47</v>
@@ -5457,10 +5439,10 @@
         <v>45</v>
       </c>
       <c r="Z52" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE52" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="AF52">
         <v>0</v>
@@ -5472,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="AL52" t="s">
-        <v>235</v>
+        <v>58</v>
       </c>
       <c r="AM52">
         <v>0</v>
@@ -5483,52 +5465,52 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="C53" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="D53">
-        <v>874072</v>
+        <v>878147</v>
       </c>
       <c r="E53">
-        <v>874071</v>
+        <v>878146</v>
       </c>
       <c r="F53" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="G53" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="H53" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I53" t="s">
-        <v>267</v>
+        <v>55</v>
       </c>
       <c r="J53" s="1">
-        <v>46022</v>
+        <v>46054</v>
       </c>
       <c r="K53" s="1">
-        <v>46022</v>
+        <v>46054</v>
       </c>
       <c r="L53">
-        <v>0.54</v>
+        <v>0.74</v>
       </c>
       <c r="M53" t="b">
         <v>1</v>
       </c>
       <c r="N53">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O53">
-        <v>960.82921320881371</v>
+        <v>2223.757224</v>
       </c>
       <c r="P53" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T53" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="W53" t="s">
         <v>47</v>
@@ -5537,10 +5519,10 @@
         <v>45</v>
       </c>
       <c r="Z53" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE53" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF53">
         <v>0</v>
@@ -5552,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="AL53" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM53">
         <v>0</v>
@@ -5563,52 +5545,52 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="C54" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="D54">
-        <v>874073</v>
+        <v>878168</v>
       </c>
       <c r="E54">
-        <v>874071</v>
+        <v>878155</v>
       </c>
       <c r="F54" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="G54" t="s">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="H54" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="I54" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J54" s="1">
-        <v>46022</v>
+        <v>46054</v>
       </c>
       <c r="K54" s="1">
-        <v>46022</v>
+        <v>46054</v>
       </c>
       <c r="L54">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>144</v>
       </c>
       <c r="O54">
-        <v>982.32292132087844</v>
+        <v>2322.0211841666701</v>
       </c>
       <c r="P54" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T54" t="s">
-        <v>182</v>
+        <v>228</v>
       </c>
       <c r="W54" t="s">
         <v>47</v>
@@ -5617,10 +5599,10 @@
         <v>45</v>
       </c>
       <c r="Z54" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE54" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF54">
         <v>0</v>
@@ -5632,7 +5614,7 @@
         <v>0</v>
       </c>
       <c r="AL54" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AM54">
         <v>0</v>
@@ -5643,52 +5625,52 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="C55" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="D55">
-        <v>874076</v>
+        <v>878180</v>
       </c>
       <c r="E55">
-        <v>874071</v>
+        <v>878175</v>
       </c>
       <c r="F55" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="G55" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="H55" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I55" t="s">
-        <v>201</v>
+        <v>55</v>
       </c>
       <c r="J55" s="1">
-        <v>46022</v>
+        <v>46054</v>
       </c>
       <c r="K55" s="1">
-        <v>46022</v>
+        <v>46054</v>
       </c>
       <c r="L55">
-        <v>1.1499999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
       </c>
       <c r="N55">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O55">
-        <v>1008.6908426417627</v>
+        <v>1105.5274420000001</v>
       </c>
       <c r="P55" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="T55" t="s">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="W55" t="s">
         <v>47</v>
@@ -5697,10 +5679,10 @@
         <v>45</v>
       </c>
       <c r="Z55" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="AE55" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF55">
         <v>0</v>
@@ -5712,9 +5694,649 @@
         <v>0</v>
       </c>
       <c r="AL55" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="AM55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>1</v>
+      </c>
+      <c r="B56" t="s">
+        <v>240</v>
+      </c>
+      <c r="C56" t="s">
+        <v>241</v>
+      </c>
+      <c r="D56">
+        <v>878185</v>
+      </c>
+      <c r="E56">
+        <v>878184</v>
+      </c>
+      <c r="F56" t="s">
+        <v>245</v>
+      </c>
+      <c r="G56" t="s">
+        <v>246</v>
+      </c>
+      <c r="H56" t="s">
+        <v>70</v>
+      </c>
+      <c r="I56" t="s">
+        <v>55</v>
+      </c>
+      <c r="J56" s="1">
+        <v>46054</v>
+      </c>
+      <c r="K56" s="1">
+        <v>46054</v>
+      </c>
+      <c r="L56">
+        <v>0.74</v>
+      </c>
+      <c r="M56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N56">
+        <v>6</v>
+      </c>
+      <c r="O56">
+        <v>1125.673632</v>
+      </c>
+      <c r="P56" t="s">
+        <v>56</v>
+      </c>
+      <c r="T56" t="s">
+        <v>247</v>
+      </c>
+      <c r="W56" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>0</v>
+      </c>
+      <c r="AH56">
+        <v>0</v>
+      </c>
+      <c r="AL56" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>1</v>
+      </c>
+      <c r="B57" t="s">
+        <v>240</v>
+      </c>
+      <c r="C57" t="s">
+        <v>241</v>
+      </c>
+      <c r="D57">
+        <v>878202</v>
+      </c>
+      <c r="E57">
+        <v>878193</v>
+      </c>
+      <c r="F57" t="s">
+        <v>250</v>
+      </c>
+      <c r="G57" t="s">
+        <v>251</v>
+      </c>
+      <c r="H57" t="s">
+        <v>97</v>
+      </c>
+      <c r="I57" t="s">
+        <v>74</v>
+      </c>
+      <c r="J57" s="1">
+        <v>46054</v>
+      </c>
+      <c r="K57" s="1">
+        <v>46054</v>
+      </c>
+      <c r="L57">
+        <v>0.48</v>
+      </c>
+      <c r="M57" t="b">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>36</v>
+      </c>
+      <c r="O57">
+        <v>1159.7253290000001</v>
+      </c>
+      <c r="P57" t="s">
+        <v>56</v>
+      </c>
+      <c r="T57" t="s">
+        <v>108</v>
+      </c>
+      <c r="W57" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE57" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>0</v>
+      </c>
+      <c r="AH57">
+        <v>0</v>
+      </c>
+      <c r="AL57" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>1</v>
+      </c>
+      <c r="B58" t="s">
+        <v>252</v>
+      </c>
+      <c r="C58" t="s">
+        <v>230</v>
+      </c>
+      <c r="D58">
+        <v>878223</v>
+      </c>
+      <c r="E58">
+        <v>878214</v>
+      </c>
+      <c r="F58" t="s">
+        <v>253</v>
+      </c>
+      <c r="G58" t="s">
+        <v>254</v>
+      </c>
+      <c r="H58" t="s">
+        <v>97</v>
+      </c>
+      <c r="I58" t="s">
+        <v>127</v>
+      </c>
+      <c r="J58" s="1">
+        <v>46051</v>
+      </c>
+      <c r="K58" s="1">
+        <v>46051</v>
+      </c>
+      <c r="L58">
+        <v>1.95</v>
+      </c>
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>9</v>
+      </c>
+      <c r="O58">
+        <v>1186.95088111111</v>
+      </c>
+      <c r="P58" t="s">
+        <v>56</v>
+      </c>
+      <c r="T58" t="s">
+        <v>255</v>
+      </c>
+      <c r="W58" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE58" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
+      <c r="AG58">
+        <v>0</v>
+      </c>
+      <c r="AH58">
+        <v>0</v>
+      </c>
+      <c r="AL58" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>1</v>
+      </c>
+      <c r="B59" t="s">
+        <v>256</v>
+      </c>
+      <c r="C59" t="s">
+        <v>230</v>
+      </c>
+      <c r="D59">
+        <v>878271</v>
+      </c>
+      <c r="E59">
+        <v>878262</v>
+      </c>
+      <c r="F59" t="s">
+        <v>253</v>
+      </c>
+      <c r="G59" t="s">
+        <v>254</v>
+      </c>
+      <c r="H59" t="s">
+        <v>97</v>
+      </c>
+      <c r="I59" t="s">
+        <v>127</v>
+      </c>
+      <c r="J59" s="1">
+        <v>46051</v>
+      </c>
+      <c r="K59" s="1">
+        <v>46051</v>
+      </c>
+      <c r="L59">
+        <v>1.95</v>
+      </c>
+      <c r="M59" t="b">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>9</v>
+      </c>
+      <c r="O59">
+        <v>1186.95088111111</v>
+      </c>
+      <c r="P59" t="s">
+        <v>56</v>
+      </c>
+      <c r="T59" t="s">
+        <v>255</v>
+      </c>
+      <c r="W59" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE59" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF59">
+        <v>0</v>
+      </c>
+      <c r="AG59">
+        <v>0</v>
+      </c>
+      <c r="AH59">
+        <v>0</v>
+      </c>
+      <c r="AL59" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1</v>
+      </c>
+      <c r="B60" t="s">
+        <v>257</v>
+      </c>
+      <c r="C60" t="s">
+        <v>230</v>
+      </c>
+      <c r="D60">
+        <v>878405</v>
+      </c>
+      <c r="E60">
+        <v>878404</v>
+      </c>
+      <c r="F60" t="s">
+        <v>258</v>
+      </c>
+      <c r="G60" t="s">
+        <v>259</v>
+      </c>
+      <c r="H60" t="s">
+        <v>70</v>
+      </c>
+      <c r="I60" t="s">
+        <v>147</v>
+      </c>
+      <c r="J60" s="1">
+        <v>46051</v>
+      </c>
+      <c r="K60" s="1">
+        <v>46051</v>
+      </c>
+      <c r="L60">
+        <v>2</v>
+      </c>
+      <c r="M60" t="b">
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <v>1</v>
+      </c>
+      <c r="O60">
+        <v>1182.5105000000001</v>
+      </c>
+      <c r="P60" t="s">
+        <v>56</v>
+      </c>
+      <c r="T60" t="s">
+        <v>260</v>
+      </c>
+      <c r="W60" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE60" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF60">
+        <v>0</v>
+      </c>
+      <c r="AG60">
+        <v>0</v>
+      </c>
+      <c r="AH60">
+        <v>0</v>
+      </c>
+      <c r="AL60" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>1</v>
+      </c>
+      <c r="B61" t="s">
+        <v>257</v>
+      </c>
+      <c r="C61" t="s">
+        <v>230</v>
+      </c>
+      <c r="D61">
+        <v>878413</v>
+      </c>
+      <c r="E61">
+        <v>878404</v>
+      </c>
+      <c r="F61" t="s">
+        <v>261</v>
+      </c>
+      <c r="G61" t="s">
+        <v>262</v>
+      </c>
+      <c r="H61" t="s">
+        <v>97</v>
+      </c>
+      <c r="I61" t="s">
+        <v>263</v>
+      </c>
+      <c r="J61" s="1">
+        <v>46051</v>
+      </c>
+      <c r="K61" s="1">
+        <v>46051</v>
+      </c>
+      <c r="L61">
+        <v>1.68</v>
+      </c>
+      <c r="M61" t="b">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>9</v>
+      </c>
+      <c r="O61">
+        <v>1186.95088111111</v>
+      </c>
+      <c r="P61" t="s">
+        <v>56</v>
+      </c>
+      <c r="T61" t="s">
+        <v>264</v>
+      </c>
+      <c r="W61" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE61" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF61">
+        <v>0</v>
+      </c>
+      <c r="AG61">
+        <v>0</v>
+      </c>
+      <c r="AH61">
+        <v>0</v>
+      </c>
+      <c r="AL61" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>1</v>
+      </c>
+      <c r="B62" t="s">
+        <v>265</v>
+      </c>
+      <c r="C62" t="s">
+        <v>230</v>
+      </c>
+      <c r="D62">
+        <v>878455</v>
+      </c>
+      <c r="E62">
+        <v>878454</v>
+      </c>
+      <c r="F62" t="s">
+        <v>258</v>
+      </c>
+      <c r="G62" t="s">
+        <v>259</v>
+      </c>
+      <c r="H62" t="s">
+        <v>70</v>
+      </c>
+      <c r="I62" t="s">
+        <v>147</v>
+      </c>
+      <c r="J62" s="1">
+        <v>46051</v>
+      </c>
+      <c r="K62" s="1">
+        <v>46051</v>
+      </c>
+      <c r="L62">
+        <v>2</v>
+      </c>
+      <c r="M62" t="b">
+        <v>1</v>
+      </c>
+      <c r="N62">
+        <v>1</v>
+      </c>
+      <c r="O62">
+        <v>1182.5105000000001</v>
+      </c>
+      <c r="P62" t="s">
+        <v>56</v>
+      </c>
+      <c r="T62" t="s">
+        <v>260</v>
+      </c>
+      <c r="W62" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE62" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF62">
+        <v>0</v>
+      </c>
+      <c r="AG62">
+        <v>0</v>
+      </c>
+      <c r="AH62">
+        <v>0</v>
+      </c>
+      <c r="AL62" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>1</v>
+      </c>
+      <c r="B63" t="s">
+        <v>266</v>
+      </c>
+      <c r="C63" t="s">
+        <v>168</v>
+      </c>
+      <c r="D63">
+        <v>878867</v>
+      </c>
+      <c r="E63">
+        <v>878856</v>
+      </c>
+      <c r="F63" t="s">
+        <v>267</v>
+      </c>
+      <c r="G63" t="s">
+        <v>268</v>
+      </c>
+      <c r="H63" t="s">
+        <v>97</v>
+      </c>
+      <c r="I63" t="s">
+        <v>263</v>
+      </c>
+      <c r="J63" s="1">
+        <v>46052</v>
+      </c>
+      <c r="K63" s="1">
+        <v>46052</v>
+      </c>
+      <c r="L63">
+        <v>2.35</v>
+      </c>
+      <c r="M63" t="b">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>96</v>
+      </c>
+      <c r="O63">
+        <v>491.53800000000001</v>
+      </c>
+      <c r="P63" t="s">
+        <v>56</v>
+      </c>
+      <c r="T63" t="s">
+        <v>269</v>
+      </c>
+      <c r="W63" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE63" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF63">
+        <v>0</v>
+      </c>
+      <c r="AG63">
+        <v>0</v>
+      </c>
+      <c r="AH63">
+        <v>0</v>
+      </c>
+      <c r="AL63" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM63">
         <v>0</v>
       </c>
     </row>
